--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17190,7 +17190,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19584,7 +19584,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20382,7 +20382,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22374,7 +22374,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23330,16 +23330,16 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="O117" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0.2570968273663853</v>
+        <v>0.3011705692006228</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -23492,10 +23492,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="O118" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24629,7 +24629,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7451</v>
+        <v>7463</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17190,7 +17190,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19584,7 +19584,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20382,7 +20382,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22374,7 +22374,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23178,7 +23178,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23330,16 +23330,16 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O117" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0.3011705692006228</v>
+        <v>0.3782996174105384</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -23492,10 +23492,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O118" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23726,16 +23726,16 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -23888,10 +23888,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7463</v>
+        <v>7485</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -20138,16 +20138,16 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="O101" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>1.336903502305204</v>
+        <v>1.355267561402802</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -20300,10 +20300,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="O102" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -23330,16 +23330,16 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="O117" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0.3782996174105384</v>
+        <v>0.4370646065228551</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -23492,10 +23492,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="O118" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -24448,6 +24448,408 @@
       <c r="BC122" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="n">
+        <v>1</v>
+      </c>
+      <c r="P123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis (Rotavirus)</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Japan NIID rotavirus gastroenteritis sentinel series.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24484,7 +24886,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -24567,7 +24969,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -24577,7 +24979,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -24597,7 +24999,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -24629,7 +25031,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7485</v>
+        <v>7507</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -1075,9 +1075,6 @@
       <c r="O4" t="n">
         <v>134</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>2.383604288957944</v>
       </c>
@@ -1471,9 +1468,6 @@
       <c r="O6" t="n">
         <v>73</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>1.29135235283072</v>
       </c>
@@ -1867,9 +1861,6 @@
       <c r="O8" t="n">
         <v>89</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.8316943581172178</v>
       </c>
@@ -2266,9 +2257,6 @@
       <c r="P10" t="n">
         <v>4</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.003267233630263065</v>
       </c>
@@ -2518,7 +2506,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2668,9 +2656,6 @@
       <c r="P12" t="n">
         <v>13</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.01061850929835496</v>
       </c>
@@ -2920,7 +2905,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3070,9 +3055,6 @@
       <c r="P14" t="n">
         <v>17</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.01388574292861803</v>
       </c>
@@ -3322,7 +3304,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3472,9 +3454,6 @@
       <c r="P16" t="n">
         <v>14</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.01143531770592073</v>
       </c>
@@ -3724,7 +3703,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4181,9 +4160,6 @@
       <c r="O20" t="n">
         <v>229</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>4.073473001278875</v>
       </c>
@@ -4580,9 +4556,6 @@
       <c r="P22" t="n">
         <v>18</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.01470255133618379</v>
       </c>
@@ -4832,7 +4805,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -4979,9 +4952,6 @@
       <c r="O24" t="n">
         <v>97</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>1.715906551021641</v>
       </c>
@@ -5375,9 +5345,6 @@
       <c r="O26" t="n">
         <v>124</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>1.158765173107135</v>
       </c>
@@ -5774,9 +5741,6 @@
       <c r="P28" t="n">
         <v>28</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.02287063541184146</v>
       </c>
@@ -6026,7 +5990,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6176,9 +6140,6 @@
       <c r="P30" t="n">
         <v>23</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.01878659337401262</v>
       </c>
@@ -6428,7 +6389,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6578,9 +6539,6 @@
       <c r="P32" t="n">
         <v>27</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.02205382700427569</v>
       </c>
@@ -6830,7 +6788,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7287,9 +7245,6 @@
       <c r="O36" t="n">
         <v>244</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>4.340294376908496</v>
       </c>
@@ -7686,9 +7641,6 @@
       <c r="P38" t="n">
         <v>30</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.02450425222697299</v>
       </c>
@@ -7938,7 +7890,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8085,9 +8037,6 @@
       <c r="O40" t="n">
         <v>160</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>2.83036132127281</v>
       </c>
@@ -8481,9 +8430,6 @@
       <c r="O42" t="n">
         <v>155</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>1.448456466383919</v>
       </c>
@@ -8880,9 +8826,6 @@
       <c r="P44" t="n">
         <v>43</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.03512276152532795</v>
       </c>
@@ -9132,7 +9075,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9282,9 +9225,6 @@
       <c r="P46" t="n">
         <v>34</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.02777148585723605</v>
       </c>
@@ -9534,7 +9474,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -9684,9 +9624,6 @@
       <c r="P48" t="n">
         <v>36</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.02940510267236759</v>
       </c>
@@ -9936,7 +9873,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10086,9 +10023,6 @@
       <c r="P50" t="n">
         <v>44</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.03593956993289372</v>
       </c>
@@ -10338,7 +10272,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10485,9 +10419,6 @@
       <c r="O52" t="n">
         <v>345</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>1.267120077734328</v>
       </c>
@@ -10647,9 +10578,6 @@
       <c r="O53" t="n">
         <v>14</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.006555452893261191</v>
       </c>
@@ -10795,9 +10723,6 @@
       <c r="O54" t="n">
         <v>151</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>2.686001848004847</v>
       </c>
@@ -11191,9 +11116,6 @@
       <c r="O56" t="n">
         <v>156</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>2.75960228824099</v>
       </c>
@@ -11587,9 +11509,6 @@
       <c r="O58" t="n">
         <v>166</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>1.551250151095036</v>
       </c>
@@ -11986,9 +11905,6 @@
       <c r="P60" t="n">
         <v>27</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.02205382700427569</v>
       </c>
@@ -12238,7 +12154,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12388,9 +12304,6 @@
       <c r="P62" t="n">
         <v>33</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.02695467744967029</v>
       </c>
@@ -12640,7 +12553,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12790,9 +12703,6 @@
       <c r="P64" t="n">
         <v>32</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.02613786904210452</v>
       </c>
@@ -13042,7 +12952,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13192,9 +13102,6 @@
       <c r="P66" t="n">
         <v>41</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.03348914471019642</v>
       </c>
@@ -13444,7 +13351,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13591,9 +13498,6 @@
       <c r="O68" t="n">
         <v>315</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>1.156935723148734</v>
       </c>
@@ -13753,9 +13657,6 @@
       <c r="O69" t="n">
         <v>97</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>1.725444895738213</v>
       </c>
@@ -14149,9 +14050,6 @@
       <c r="O71" t="n">
         <v>148</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>2.618084222177349</v>
       </c>
@@ -14545,9 +14443,6 @@
       <c r="O73" t="n">
         <v>136</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>1.270903738246535</v>
       </c>
@@ -14944,9 +14839,6 @@
       <c r="P75" t="n">
         <v>37</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.03022191107993335</v>
       </c>
@@ -15196,7 +15088,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -15346,9 +15238,6 @@
       <c r="P77" t="n">
         <v>30</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.02450425222697299</v>
       </c>
@@ -15598,7 +15487,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -15748,9 +15637,6 @@
       <c r="P79" t="n">
         <v>30</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.02450425222697299</v>
       </c>
@@ -16000,7 +15886,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -16150,9 +16036,6 @@
       <c r="P81" t="n">
         <v>25</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.02042021018914416</v>
       </c>
@@ -16402,7 +16285,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -16552,9 +16435,6 @@
       <c r="P83" t="n">
         <v>23</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.01878659337401262</v>
       </c>
@@ -16804,7 +16684,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -16951,9 +16831,6 @@
       <c r="O85" t="n">
         <v>244</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.8961660839628288</v>
       </c>
@@ -17347,9 +17224,6 @@
       <c r="O87" t="n">
         <v>52</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.9249807688493514</v>
       </c>
@@ -17743,9 +17617,6 @@
       <c r="O89" t="n">
         <v>103</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>1.822045100569371</v>
       </c>
@@ -18139,9 +18010,6 @@
       <c r="O91" t="n">
         <v>102</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.9531778036849013</v>
       </c>
@@ -18538,9 +18406,6 @@
       <c r="P93" t="n">
         <v>17</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.01388574292861803</v>
       </c>
@@ -18790,7 +18655,7 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN94" t="b">
@@ -18940,9 +18805,6 @@
       <c r="P95" t="n">
         <v>15</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.01225212611348649</v>
       </c>
@@ -19192,7 +19054,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -19342,9 +19204,6 @@
       <c r="P97" t="n">
         <v>10</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.008168084075657663</v>
       </c>
@@ -19594,7 +19453,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -19744,9 +19603,6 @@
       <c r="P99" t="n">
         <v>14</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.01143531770592073</v>
       </c>
@@ -19996,7 +19852,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -20143,9 +19999,6 @@
       <c r="O101" t="n">
         <v>369</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>1.355267561402802</v>
       </c>
@@ -20539,9 +20392,6 @@
       <c r="O103" t="n">
         <v>21</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.3735499258814688</v>
       </c>
@@ -20935,9 +20785,6 @@
       <c r="O105" t="n">
         <v>56</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.9906264624454836</v>
       </c>
@@ -21331,9 +21178,6 @@
       <c r="O107" t="n">
         <v>64</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.5980723474101342</v>
       </c>
@@ -21730,9 +21574,6 @@
       <c r="P109" t="n">
         <v>19</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.01551935974374956</v>
       </c>
@@ -21982,7 +21823,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -22132,9 +21973,6 @@
       <c r="P111" t="n">
         <v>8</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.00653446726052613</v>
       </c>
@@ -22384,7 +22222,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -22534,9 +22372,6 @@
       <c r="P113" t="n">
         <v>9</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.007351275668091897</v>
       </c>
@@ -22786,7 +22621,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -22936,9 +22771,6 @@
       <c r="P115" t="n">
         <v>9</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.007351275668091897</v>
       </c>
@@ -23188,7 +23020,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -23335,9 +23167,6 @@
       <c r="O117" t="n">
         <v>119</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.4370646065228551</v>
       </c>
@@ -23731,9 +23560,6 @@
       <c r="O119" t="n">
         <v>2</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -24122,16 +23948,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="O121" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R121" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.3007258903852361</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -24284,10 +24107,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="O122" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -24526,9 +24349,6 @@
       <c r="P123" t="n">
         <v>1</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -24778,7 +24598,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25031,7 +24851,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7507</v>
+        <v>7518</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -23162,13 +23162,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="O117" t="n">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="R117" t="n">
-        <v>0.4370646065228551</v>
+        <v>0.5509217729279685</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -23321,10 +23321,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="O118" t="n">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -23555,13 +23555,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O119" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R119" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -23714,10 +23714,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O120" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7518</v>
+        <v>7551</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -23162,13 +23162,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="O117" t="n">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="R117" t="n">
-        <v>0.5509217729279685</v>
+        <v>0.6500876920550028</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -23321,10 +23321,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="O118" t="n">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7551</v>
+        <v>7578</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -23162,13 +23162,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="O117" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="R117" t="n">
-        <v>0.6500876920550028</v>
+        <v>0.7088526811673195</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -23321,10 +23321,10 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="O118" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
@@ -23555,13 +23555,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O119" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R119" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -23714,10 +23714,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O120" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -24668,6 +24668,405 @@
         </is>
       </c>
       <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="P125" t="n">
+        <v>1</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+      <c r="P126" t="n">
+        <v>1</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis (Rotavirus)</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Japan NIID rotavirus gastroenteritis sentinel series.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -24706,7 +25105,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -24789,7 +25188,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -24799,7 +25198,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">
@@ -24819,7 +25218,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -24851,7 +25250,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7578</v>
+        <v>7597</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -17077,7 +17077,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -20245,7 +20245,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -23555,13 +23555,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O119" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R119" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -23714,10 +23714,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O120" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7597</v>
+        <v>7598</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -19994,13 +19994,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O101" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="R101" t="n">
-        <v>1.355267561402802</v>
+        <v>1.358940373222322</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -20153,10 +20153,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O102" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -23948,13 +23948,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="O121" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="R121" t="n">
-        <v>0.3007258903852361</v>
+        <v>0.548382505996607</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -24107,10 +24107,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="O122" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7598</v>
+        <v>7613</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -23555,13 +23555,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O119" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R119" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -23714,10 +23714,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O120" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -23948,13 +23948,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="O121" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="R121" t="n">
-        <v>0.548382505996607</v>
+        <v>0.7960391216079779</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -24107,10 +24107,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="O122" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -25067,6 +25067,405 @@
         </is>
       </c>
       <c r="BC126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>8</v>
+      </c>
+      <c r="O127" t="n">
+        <v>8</v>
+      </c>
+      <c r="P127" t="n">
+        <v>8</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>rotavirus-infection</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D199</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Rotavirus infection</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>轮状病毒感染</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>8</v>
+      </c>
+      <c r="O128" t="n">
+        <v>8</v>
+      </c>
+      <c r="P128" t="n">
+        <v>8</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis (Rotavirus)</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Japan NIID rotavirus gastroenteritis sentinel series.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN128" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_JP_ROTAVIRUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -25105,7 +25504,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -25188,7 +25587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -25198,7 +25597,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -25218,7 +25617,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -25250,7 +25649,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7613</v>
+        <v>7637</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18645,7 +18645,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -19044,7 +19044,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21813,7 +21813,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23010,7 +23010,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24987,7 +24987,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18645,7 +18645,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -19044,7 +19044,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21813,7 +21813,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23010,7 +23010,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24987,7 +24987,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18645,7 +18645,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -19044,7 +19044,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21813,7 +21813,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23010,7 +23010,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24987,7 +24987,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -18645,7 +18645,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -19044,7 +19044,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21813,7 +21813,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -23010,7 +23010,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24987,7 +24987,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">

--- a/diseases/d199/2026-2029.xlsx
+++ b/diseases/d199/2026-2029.xlsx
@@ -28351,13 +28351,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="O148" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="R148" t="n">
-        <v>0.04040093001471769</v>
+        <v>0.08080186002943539</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -28510,10 +28510,10 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="O149" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8598</v>
+        <v>8609</v>
       </c>
     </row>
     <row r="16">
